--- a/Hypothesis2_Results.xlsx
+++ b/Hypothesis2_Results.xlsx
@@ -458,7 +458,7 @@
         <v>219552536.6421293</v>
       </c>
       <c r="C2" t="n">
-        <v>44630905.87724537</v>
+        <v>41271454.22117331</v>
       </c>
       <c r="D2" t="n">
         <v>322420046.3326892</v>
@@ -472,7 +472,7 @@
         <v>153985774.6617198</v>
       </c>
       <c r="C3" t="n">
-        <v>42864478.019345</v>
+        <v>40709075.08109524</v>
       </c>
       <c r="D3" t="n">
         <v>322388365.0407007</v>
@@ -486,7 +486,7 @@
         <v>112126111.8639931</v>
       </c>
       <c r="C4" t="n">
-        <v>46376527.04930638</v>
+        <v>39861391.62875098</v>
       </c>
       <c r="D4" t="n">
         <v>322356689.402055</v>
@@ -500,7 +500,7 @@
         <v>85354551.9657221</v>
       </c>
       <c r="C5" t="n">
-        <v>39040038.46871154</v>
+        <v>39652337.77914666</v>
       </c>
       <c r="D5" t="n">
         <v>322325019.5098291</v>
@@ -514,7 +514,7 @@
         <v>68204709.87889802</v>
       </c>
       <c r="C6" t="n">
-        <v>42014373.83712491</v>
+        <v>42749567.19211265</v>
       </c>
       <c r="D6" t="n">
         <v>322293355.4561927</v>
@@ -528,7 +528,7 @@
         <v>57201699.51271682</v>
       </c>
       <c r="C7" t="n">
-        <v>39475374.41279361</v>
+        <v>39346484.70495919</v>
       </c>
       <c r="D7" t="n">
         <v>322261697.3322101</v>
@@ -542,7 +542,7 @@
         <v>50132080.99635869</v>
       </c>
       <c r="C8" t="n">
-        <v>39287429.56127426</v>
+        <v>40691761.32014612</v>
       </c>
       <c r="D8" t="n">
         <v>322230045.2276496</v>
@@ -556,7 +556,7 @@
         <v>45583335.74807096</v>
       </c>
       <c r="C9" t="n">
-        <v>41079488.6916072</v>
+        <v>40596481.4433451</v>
       </c>
       <c r="D9" t="n">
         <v>322198399.2308013</v>
@@ -570,7 +570,7 @@
         <v>42652540.61713104</v>
       </c>
       <c r="C10" t="n">
-        <v>43153910.35774432</v>
+        <v>38163335.34114879</v>
       </c>
       <c r="D10" t="n">
         <v>322166759.4283065</v>
@@ -584,7 +584,7 @@
         <v>40761621.59005164</v>
       </c>
       <c r="C11" t="n">
-        <v>45327569.0848319</v>
+        <v>41924660.65081222</v>
       </c>
       <c r="D11" t="n">
         <v>322135125.9049968</v>
@@ -598,7 +598,7 @@
         <v>39539940.508566</v>
       </c>
       <c r="C12" t="n">
-        <v>40102377.57494654</v>
+        <v>40247601.69285557</v>
       </c>
       <c r="D12" t="n">
         <v>322103498.7437466</v>
@@ -612,7 +612,7 @@
         <v>38749529.3309104</v>
       </c>
       <c r="C13" t="n">
-        <v>40654344.42829435</v>
+        <v>42417508.81391865</v>
       </c>
       <c r="D13" t="n">
         <v>322071878.0253382</v>
@@ -626,7 +626,7 @@
         <v>38237397.45166172</v>
       </c>
       <c r="C14" t="n">
-        <v>40581504.99990487</v>
+        <v>40292094.89796501</v>
       </c>
       <c r="D14" t="n">
         <v>322040263.8283406</v>
@@ -640,7 +640,7 @@
         <v>37905059.68780299</v>
       </c>
       <c r="C15" t="n">
-        <v>41196118.0646444</v>
+        <v>38749235.44206754</v>
       </c>
       <c r="D15" t="n">
         <v>322008656.2290021</v>
@@ -654,7 +654,7 @@
         <v>37689037.78127919</v>
       </c>
       <c r="C16" t="n">
-        <v>41198541.5158042</v>
+        <v>41727771.5226258</v>
       </c>
       <c r="D16" t="n">
         <v>321977055.3011574</v>
@@ -668,7 +668,7 @@
         <v>37548366.07293484</v>
       </c>
       <c r="C17" t="n">
-        <v>40125402.51165953</v>
+        <v>40973040.28562903</v>
       </c>
       <c r="D17" t="n">
         <v>321945461.1161488</v>
@@ -682,7 +682,7 @@
         <v>37456574.60948081</v>
       </c>
       <c r="C18" t="n">
-        <v>40255227.81257837</v>
+        <v>39255348.53807478</v>
       </c>
       <c r="D18" t="n">
         <v>321913873.7427623</v>
@@ -696,7 +696,7 @@
         <v>37396538.54478128</v>
       </c>
       <c r="C19" t="n">
-        <v>39556609.68042865</v>
+        <v>38203269.59047475</v>
       </c>
       <c r="D19" t="n">
         <v>321882293.2471768</v>
@@ -710,7 +710,7 @@
         <v>37357164.92148819</v>
       </c>
       <c r="C20" t="n">
-        <v>42696700.37087946</v>
+        <v>40709544.01391978</v>
       </c>
       <c r="D20" t="n">
         <v>321850719.6929274</v>
@@ -724,7 +724,7 @@
         <v>37331258.79145281</v>
       </c>
       <c r="C21" t="n">
-        <v>41727104.85786451</v>
+        <v>40040854.43093591</v>
       </c>
       <c r="D21" t="n">
         <v>321819153.1408826</v>
@@ -738,7 +738,7 @@
         <v>37314147.24988513</v>
       </c>
       <c r="C22" t="n">
-        <v>42395016.42030559</v>
+        <v>39228640.53873999</v>
       </c>
       <c r="D22" t="n">
         <v>321787593.649233</v>
@@ -752,7 +752,7 @@
         <v>37302791.14145322</v>
       </c>
       <c r="C23" t="n">
-        <v>41846178.72429699</v>
+        <v>40085376.56265154</v>
       </c>
       <c r="D23" t="n">
         <v>321756041.2734929</v>
@@ -766,7 +766,7 @@
         <v>37295210.92665201</v>
       </c>
       <c r="C24" t="n">
-        <v>38811880.71921522</v>
+        <v>41559798.28347588</v>
       </c>
       <c r="D24" t="n">
         <v>321724496.0665122</v>
@@ -780,7 +780,7 @@
         <v>37290115.16798721</v>
       </c>
       <c r="C25" t="n">
-        <v>41764200.74940873</v>
+        <v>40029155.48336121</v>
       </c>
       <c r="D25" t="n">
         <v>321692958.0784999</v>
@@ -794,7 +794,7 @@
         <v>37286659.84809084</v>
       </c>
       <c r="C26" t="n">
-        <v>40531531.82121707</v>
+        <v>45303286.33194987</v>
       </c>
       <c r="D26" t="n">
         <v>321661427.3570561</v>
@@ -808,7 +808,7 @@
         <v>37284292.26298852</v>
       </c>
       <c r="C27" t="n">
-        <v>41839064.5324825</v>
+        <v>41401227.97314633</v>
       </c>
       <c r="D27" t="n">
         <v>321629903.9472133</v>
@@ -822,7 +822,7 @@
         <v>37282649.65057652</v>
       </c>
       <c r="C28" t="n">
-        <v>39794709.35063527</v>
+        <v>43069694.9414097</v>
       </c>
       <c r="D28" t="n">
         <v>321598387.8914854</v>
@@ -836,7 +836,7 @@
         <v>37281493.28289445</v>
       </c>
       <c r="C29" t="n">
-        <v>40716418.77279687</v>
+        <v>38968259.18344551</v>
       </c>
       <c r="D29" t="n">
         <v>321566879.2299234</v>
@@ -850,7 +850,7 @@
         <v>37280665.56218078</v>
       </c>
       <c r="C30" t="n">
-        <v>40676315.40745094</v>
+        <v>40001863.1432227</v>
       </c>
       <c r="D30" t="n">
         <v>321535378.0001775</v>
@@ -864,7 +864,7 @@
         <v>37280062.05560242</v>
       </c>
       <c r="C31" t="n">
-        <v>42818112.79516345</v>
+        <v>39661292.97298206</v>
       </c>
       <c r="D31" t="n">
         <v>321503884.2375643</v>
@@ -878,7 +878,7 @@
         <v>37279613.24244139</v>
       </c>
       <c r="C32" t="n">
-        <v>41660695.2040702</v>
+        <v>39772989.88677602</v>
       </c>
       <c r="D32" t="n">
         <v>321472397.9751377</v>
@@ -892,7 +892,7 @@
         <v>37279272.58334443</v>
       </c>
       <c r="C33" t="n">
-        <v>42475319.52683529</v>
+        <v>44515310.85457195</v>
       </c>
       <c r="D33" t="n">
         <v>321440919.2437645</v>
@@ -906,7 +906,7 @@
         <v>37279008.709726</v>
       </c>
       <c r="C34" t="n">
-        <v>39948031.5457726</v>
+        <v>41747960.81087033</v>
       </c>
       <c r="D34" t="n">
         <v>321409448.072202</v>
@@ -920,7 +920,7 @@
         <v>37278800.30167103</v>
       </c>
       <c r="C35" t="n">
-        <v>40559183.49998126</v>
+        <v>39542376.76408254</v>
       </c>
       <c r="D35" t="n">
         <v>321377984.4871777</v>
@@ -934,7 +934,7 @@
         <v>37278632.72243503</v>
       </c>
       <c r="C36" t="n">
-        <v>38890131.97094933</v>
+        <v>42183140.1488806</v>
       </c>
       <c r="D36" t="n">
         <v>321346528.5134708</v>
@@ -948,7 +948,7 @@
         <v>37278495.80224102</v>
       </c>
       <c r="C37" t="n">
-        <v>42984710.18980915</v>
+        <v>38477694.52474163</v>
       </c>
       <c r="D37" t="n">
         <v>321315080.1739943</v>
@@ -962,7 +962,7 @@
         <v>37278382.3751436</v>
       </c>
       <c r="C38" t="n">
-        <v>42744938.43226997</v>
+        <v>40183103.89890357</v>
       </c>
       <c r="D38" t="n">
         <v>321283639.4898772</v>
@@ -976,7 +976,7 @@
         <v>37278287.31012876</v>
       </c>
       <c r="C39" t="n">
-        <v>41953909.15315782</v>
+        <v>40633362.10324594</v>
       </c>
       <c r="D39" t="n">
         <v>321252206.4805469</v>
@@ -990,7 +990,7 @@
         <v>37278206.86716002</v>
       </c>
       <c r="C40" t="n">
-        <v>40858583.91786718</v>
+        <v>41588681.82272869</v>
       </c>
       <c r="D40" t="n">
         <v>321220781.1638106</v>
@@ -1004,7 +1004,7 @@
         <v>37278138.26730059</v>
       </c>
       <c r="C41" t="n">
-        <v>42359563.88617555</v>
+        <v>40831484.47899295</v>
       </c>
       <c r="D41" t="n">
         <v>321189363.5559355</v>
@@ -1018,7 +1018,7 @@
         <v>37278079.40419897</v>
       </c>
       <c r="C42" t="n">
-        <v>38737769.06172043</v>
+        <v>41627758.24027107</v>
       </c>
       <c r="D42" t="n">
         <v>321157953.6717281</v>
@@ -1032,7 +1032,7 @@
         <v>37278028.64917834</v>
       </c>
       <c r="C43" t="n">
-        <v>40475239.73976856</v>
+        <v>42265684.51473735</v>
       </c>
       <c r="D43" t="n">
         <v>321126551.5246111</v>
@@ -1046,7 +1046,7 @@
         <v>37277984.71850804</v>
       </c>
       <c r="C44" t="n">
-        <v>40985831.76895084</v>
+        <v>43018318.32159541</v>
       </c>
       <c r="D44" t="n">
         <v>321095157.1266987</v>
@@ -1060,7 +1060,7 @@
         <v>37277946.58214505</v>
       </c>
       <c r="C45" t="n">
-        <v>43747807.22413635</v>
+        <v>39226902.54532265</v>
       </c>
       <c r="D45" t="n">
         <v>321063770.48887</v>
@@ -1074,7 +1074,7 @@
         <v>37277913.40026445</v>
       </c>
       <c r="C46" t="n">
-        <v>39958278.38373831</v>
+        <v>40246775.59675324</v>
       </c>
       <c r="D46" t="n">
         <v>321032391.6208397</v>
@@ -1088,7 +1088,7 @@
         <v>37277884.47851945</v>
       </c>
       <c r="C47" t="n">
-        <v>43450014.26035521</v>
+        <v>41842805.18238026</v>
       </c>
       <c r="D47" t="n">
         <v>321001020.5312254</v>
@@ -1102,7 +1102,7 @@
         <v>37277859.23601426</v>
       </c>
       <c r="C48" t="n">
-        <v>39998050.46259851</v>
+        <v>40624320.77093909</v>
       </c>
       <c r="D48" t="n">
         <v>320969657.2276149</v>
@@ -1116,7 +1116,7 @@
         <v>37277837.18198029</v>
       </c>
       <c r="C49" t="n">
-        <v>39811255.78878737</v>
+        <v>39818753.04091135</v>
       </c>
       <c r="D49" t="n">
         <v>320938301.7166275</v>
@@ -1130,7 +1130,7 @@
         <v>37277817.89847201</v>
       </c>
       <c r="C50" t="n">
-        <v>40642607.4566915</v>
+        <v>46278822.54780504</v>
       </c>
       <c r="D50" t="n">
         <v>320906954.0039752</v>
@@ -1144,7 +1144,7 @@
         <v>37277801.02727761</v>
       </c>
       <c r="C51" t="n">
-        <v>43895699.34327947</v>
+        <v>46657725.09913495</v>
       </c>
       <c r="D51" t="n">
         <v>320875614.0945202</v>
